--- a/moduli_aziende/luppichiniulisse/moduli_compilati/MOD-910-C-Soddisfazione_Clienti.xlsx
+++ b/moduli_aziende/luppichiniulisse/moduli_compilati/MOD-910-C-Soddisfazione_Clienti.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simoneleandrini\Documents\GitHub\SG_Viewer\moduli_aziende\luppichiniulisse\moduli_compilati\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC290C3-04C9-4A17-B207-4106AA856CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="16">
   <si>
     <t>Data</t>
   </si>
@@ -40,23 +59,35 @@
     <t>Check</t>
   </si>
   <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
     <t>Qualità</t>
   </si>
   <si>
     <t>ok</t>
+  </si>
+  <si>
+    <t>. . Dato non disponibile in modalità ospite . .</t>
+  </si>
+  <si>
+    <t>Puntualità</t>
+  </si>
+  <si>
+    <t>Economicità dimostrata</t>
+  </si>
+  <si>
+    <t>Supporto post-vendita</t>
+  </si>
+  <si>
+    <t>Supporto richieste specifiche</t>
+  </si>
+  <si>
+    <t>n.a.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,24 +139,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -163,7 +203,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -197,6 +237,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -231,9 +272,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -406,11 +448,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -436,30 +487,949 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
       <c r="E2">
-        <v>1</v>
+        <f ca="1">RANDBETWEEN(4,5)</f>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E36" ca="1" si="0">RANDBETWEEN(4,5)</f>
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F33" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>46367</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
